--- a/supporting_material/experiments/template/template-dual-display.xlsx
+++ b/supporting_material/experiments/template/template-dual-display.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adrianomartinelli/projects/delt-hit/supporting_material/experiments/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E772160-C61F-E04F-AB80-28D384A1CEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5A801A-ADB2-3847-BC3F-33696CE13D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1600" windowWidth="27220" windowHeight="17080" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8340" yWindow="660" windowWidth="21900" windowHeight="18980" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="experiment" sheetId="8" r:id="rId1"/>
@@ -46,10 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="134">
-  <si>
-    <t>GCCTCG</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="136">
   <si>
     <t>ACTCTG</t>
   </si>
@@ -327,9 +324,6 @@
     <t>CGCTCT</t>
   </si>
   <si>
-    <t>TCCGAC</t>
-  </si>
-  <si>
     <t>ATGCGT</t>
   </si>
   <si>
@@ -339,15 +333,9 @@
     <t>TCGATA</t>
   </si>
   <si>
-    <t>SR</t>
-  </si>
-  <si>
     <t>[#6:1][$([NX2-][NX2+]#[NX1]),$([NX2]=[NX2+]=[NX1-])]&gt;&gt;[#6:1][N;H2]</t>
   </si>
   <si>
-    <t>CuAAC</t>
-  </si>
-  <si>
     <t>[CX2:1]#[CX2;H1:2].[N:3]=[N+:4]=[N-:5]&gt;&gt;[C:1]1=[C:2][N-0:3][N-0:4]=[N-0:5]1</t>
   </si>
   <si>
@@ -372,12 +360,6 @@
     <t>CC(C)(CN)CN1CCCCCC1</t>
   </si>
   <si>
-    <t>OC(=O)COC1=C2C=CC=CC2=CC=C1</t>
-  </si>
-  <si>
-    <t>CC1=CC2=C(SCC(O)=O)N=CN=C2S1</t>
-  </si>
-  <si>
     <t>C#CCN1C=CC2=C1C=CC=C2</t>
   </si>
   <si>
@@ -396,12 +378,6 @@
     <t>educt_2</t>
   </si>
   <si>
-    <t>ABF1</t>
-  </si>
-  <si>
-    <t>ABF2</t>
-  </si>
-  <si>
     <t>[CX3:1](=[O:2])[OX2;H1].[N;$([N;H1,H2]),$([N;H3]);!$([N;H1,H2][S]);!$([NX3][CX3](=[OX1])[#6]);!$([NX3][CX3](=[OX1])[OX2]):4]&gt;&gt;[CX3:1](=[O:2])[N:4]</t>
   </si>
   <si>
@@ -448,6 +424,36 @@
   </si>
   <si>
     <t>campaign-dual.fastq.gz</t>
+  </si>
+  <si>
+    <t>strand</t>
+  </si>
+  <si>
+    <t>product_4</t>
+  </si>
+  <si>
+    <t>A-ABF1</t>
+  </si>
+  <si>
+    <t>A-ABF2</t>
+  </si>
+  <si>
+    <t>A-SR</t>
+  </si>
+  <si>
+    <t>A-CuAAC</t>
+  </si>
+  <si>
+    <t>B-ABF1</t>
+  </si>
+  <si>
+    <t>B-ABF2</t>
+  </si>
+  <si>
+    <t>B-SR</t>
+  </si>
+  <si>
+    <t>B-CuAAC</t>
   </si>
 </sst>
 </file>
@@ -592,7 +598,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -662,26 +668,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -937,7 +923,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -948,7 +934,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -958,118 +944,113 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1081,25 +1062,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1304,42 +1287,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>127</v>
+      <c r="A2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>126</v>
+      <c r="B4" s="15" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="19">
+      <c r="A5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="17">
         <v>11</v>
       </c>
     </row>
@@ -1350,52 +1333,84 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="103.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="108.5" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="10.6640625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>16</v>
+      <c r="A1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="52" t="s">
-        <v>118</v>
+      <c r="A2" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>118</v>
+      <c r="A3" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>98</v>
+      <c r="A4" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>100</v>
+      <c r="A5" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1416,48 +1431,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="65" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="66" t="s">
-        <v>53</v>
+      <c r="A1" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="45"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="63"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="63"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="63"/>
-      <c r="B7" s="63"/>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -1481,628 +1496,628 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="20" t="s">
+      <c r="E1" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="E2" s="22"/>
+      <c r="F2" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="48">
+      <c r="B3" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="46">
         <v>45561</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D3" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="22"/>
+      <c r="F3" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="48">
+      <c r="E5" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="46">
         <v>45561</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D6" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="24"/>
-      <c r="F3" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="48">
+      <c r="E6" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="46">
         <v>45561</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D7" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="25" t="s">
+      <c r="E7" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="48">
+      <c r="G7" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="46">
         <v>45561</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="25" t="s">
+      <c r="D8" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="46">
+        <v>45561</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="22"/>
+      <c r="F21" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="22"/>
+      <c r="F22" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D11" s="24" t="s">
+      <c r="G25" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D26" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D12" s="24" t="s">
+      <c r="E26" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="46">
+        <v>45582</v>
+      </c>
+      <c r="D27" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="24"/>
-      <c r="F12" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D13" s="24" t="s">
+      <c r="E27" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="49">
+        <v>45582</v>
+      </c>
+      <c r="D28" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="49" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C18" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="48">
-        <v>45561</v>
-      </c>
-      <c r="D19" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C22" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="49" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="48">
-        <v>45582</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="F27" s="25" t="s">
+      <c r="E28" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="G27" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="51">
-        <v>45582</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="34" t="s">
-        <v>96</v>
+      <c r="G28" s="32" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -3872,7 +3887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB600AC-AAF2-E34D-85F6-8C16A5641E8B}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="7" bestFit="1" customWidth="1"/>
@@ -3882,173 +3897,195 @@
     <col min="5" max="16384" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="72" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="67" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="68">
+        <v>0</v>
+      </c>
+      <c r="D2" s="68" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="69"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="B3" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="65">
+        <v>1.01</v>
+      </c>
+      <c r="D3" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="50"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="65">
+        <v>0</v>
+      </c>
+      <c r="D4" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="65">
+        <v>1.01</v>
+      </c>
+      <c r="D5" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="50"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="65">
+        <v>0</v>
+      </c>
+      <c r="D6" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="65">
+        <v>1.01</v>
+      </c>
+      <c r="D7" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="50"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="65">
+        <v>0</v>
+      </c>
+      <c r="D8" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="65">
+        <v>1.01</v>
+      </c>
+      <c r="D9" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="65">
+        <v>0</v>
+      </c>
+      <c r="D10" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="65">
+        <v>1.01</v>
+      </c>
+      <c r="D11" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="50"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="66" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="C12" s="66">
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="b">
+      <c r="D12" s="66" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D3" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D5" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D7" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D9" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="D11" s="9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11" t="b">
-        <v>0</v>
-      </c>
+      <c r="E12" s="37"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -4069,50 +4106,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4134,131 +4171,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="41"/>
+      <c r="E1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="A2" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="68" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="A3" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="A4" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="67" t="s">
+      <c r="A5" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
+      <c r="A6" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>106</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
@@ -4371,464 +4408,464 @@
       <c r="J190" s="2"/>
     </row>
     <row r="191" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H191" s="40"/>
-      <c r="I191" s="40"/>
+      <c r="H191" s="38"/>
+      <c r="I191" s="38"/>
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
     </row>
     <row r="192" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H192" s="40"/>
-      <c r="I192" s="40"/>
+      <c r="H192" s="38"/>
+      <c r="I192" s="38"/>
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
     </row>
     <row r="193" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H193" s="40"/>
-      <c r="I193" s="40"/>
+      <c r="H193" s="38"/>
+      <c r="I193" s="38"/>
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
     </row>
     <row r="194" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H194" s="40"/>
-      <c r="I194" s="40"/>
+      <c r="H194" s="38"/>
+      <c r="I194" s="38"/>
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
     </row>
     <row r="195" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H195" s="40"/>
-      <c r="I195" s="40"/>
+      <c r="H195" s="38"/>
+      <c r="I195" s="38"/>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
     </row>
     <row r="196" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H196" s="40"/>
-      <c r="I196" s="40"/>
+      <c r="H196" s="38"/>
+      <c r="I196" s="38"/>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
     </row>
     <row r="197" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H197" s="40"/>
-      <c r="I197" s="40"/>
+      <c r="H197" s="38"/>
+      <c r="I197" s="38"/>
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
     </row>
     <row r="198" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H198" s="40"/>
-      <c r="I198" s="40"/>
+      <c r="H198" s="38"/>
+      <c r="I198" s="38"/>
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
     </row>
     <row r="199" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H199" s="40"/>
-      <c r="I199" s="40"/>
+      <c r="H199" s="38"/>
+      <c r="I199" s="38"/>
       <c r="J199" s="2"/>
       <c r="K199" s="2"/>
     </row>
     <row r="200" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H200" s="40"/>
-      <c r="I200" s="40"/>
+      <c r="H200" s="38"/>
+      <c r="I200" s="38"/>
       <c r="J200" s="2"/>
       <c r="K200" s="2"/>
     </row>
     <row r="201" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H201" s="40"/>
-      <c r="I201" s="40"/>
+      <c r="H201" s="38"/>
+      <c r="I201" s="38"/>
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
     </row>
     <row r="202" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H202" s="40"/>
-      <c r="I202" s="40"/>
+      <c r="H202" s="38"/>
+      <c r="I202" s="38"/>
       <c r="J202" s="2"/>
       <c r="K202" s="2"/>
     </row>
     <row r="203" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H203" s="40"/>
-      <c r="I203" s="40"/>
+      <c r="H203" s="38"/>
+      <c r="I203" s="38"/>
       <c r="J203" s="2"/>
       <c r="K203" s="2"/>
     </row>
     <row r="204" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H204" s="40"/>
-      <c r="I204" s="40"/>
+      <c r="H204" s="38"/>
+      <c r="I204" s="38"/>
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
     </row>
     <row r="205" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H205" s="40"/>
-      <c r="I205" s="40"/>
+      <c r="H205" s="38"/>
+      <c r="I205" s="38"/>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
     </row>
     <row r="206" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H206" s="40"/>
-      <c r="I206" s="40"/>
+      <c r="H206" s="38"/>
+      <c r="I206" s="38"/>
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
     </row>
     <row r="207" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H207" s="40"/>
-      <c r="I207" s="40"/>
+      <c r="H207" s="38"/>
+      <c r="I207" s="38"/>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
     </row>
     <row r="208" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H208" s="40"/>
-      <c r="I208" s="40"/>
+      <c r="H208" s="38"/>
+      <c r="I208" s="38"/>
       <c r="J208" s="2"/>
       <c r="K208" s="2"/>
     </row>
     <row r="209" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H209" s="40"/>
-      <c r="I209" s="40"/>
+      <c r="H209" s="38"/>
+      <c r="I209" s="38"/>
       <c r="J209" s="2"/>
       <c r="K209" s="2"/>
     </row>
     <row r="210" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H210" s="40"/>
-      <c r="I210" s="40"/>
+      <c r="H210" s="38"/>
+      <c r="I210" s="38"/>
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
     </row>
     <row r="211" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H211" s="40"/>
-      <c r="I211" s="40"/>
+      <c r="H211" s="38"/>
+      <c r="I211" s="38"/>
       <c r="J211" s="2"/>
       <c r="K211" s="2"/>
     </row>
     <row r="212" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H212" s="40"/>
-      <c r="I212" s="40"/>
+      <c r="H212" s="38"/>
+      <c r="I212" s="38"/>
       <c r="J212" s="2"/>
       <c r="K212" s="2"/>
     </row>
     <row r="213" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H213" s="40"/>
-      <c r="I213" s="40"/>
+      <c r="H213" s="38"/>
+      <c r="I213" s="38"/>
       <c r="J213" s="2"/>
       <c r="K213" s="2"/>
     </row>
     <row r="214" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H214" s="40"/>
-      <c r="I214" s="40"/>
+      <c r="H214" s="38"/>
+      <c r="I214" s="38"/>
       <c r="J214" s="2"/>
       <c r="K214" s="2"/>
     </row>
     <row r="215" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H215" s="40"/>
-      <c r="I215" s="40"/>
+      <c r="H215" s="38"/>
+      <c r="I215" s="38"/>
       <c r="J215" s="2"/>
       <c r="K215" s="2"/>
     </row>
     <row r="216" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H216" s="40"/>
-      <c r="I216" s="40"/>
+      <c r="H216" s="38"/>
+      <c r="I216" s="38"/>
       <c r="J216" s="2"/>
       <c r="K216" s="2"/>
     </row>
     <row r="217" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H217" s="40"/>
-      <c r="I217" s="40"/>
+      <c r="H217" s="38"/>
+      <c r="I217" s="38"/>
       <c r="J217" s="2"/>
       <c r="K217" s="2"/>
     </row>
     <row r="218" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H218" s="40"/>
-      <c r="I218" s="40"/>
+      <c r="H218" s="38"/>
+      <c r="I218" s="38"/>
       <c r="J218" s="2"/>
       <c r="K218" s="2"/>
     </row>
     <row r="219" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H219" s="40"/>
-      <c r="I219" s="40"/>
+      <c r="H219" s="38"/>
+      <c r="I219" s="38"/>
       <c r="J219" s="2"/>
       <c r="K219" s="2"/>
     </row>
     <row r="220" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H220" s="40"/>
-      <c r="I220" s="40"/>
+      <c r="H220" s="38"/>
+      <c r="I220" s="38"/>
       <c r="J220" s="2"/>
       <c r="K220" s="2"/>
     </row>
     <row r="221" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H221" s="40"/>
-      <c r="I221" s="40"/>
+      <c r="H221" s="38"/>
+      <c r="I221" s="38"/>
       <c r="J221" s="2"/>
       <c r="K221" s="2"/>
     </row>
     <row r="222" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H222" s="40"/>
-      <c r="I222" s="40"/>
+      <c r="H222" s="38"/>
+      <c r="I222" s="38"/>
       <c r="J222" s="2"/>
       <c r="K222" s="2"/>
     </row>
     <row r="223" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H223" s="40"/>
-      <c r="I223" s="40"/>
+      <c r="H223" s="38"/>
+      <c r="I223" s="38"/>
       <c r="J223" s="2"/>
       <c r="K223" s="2"/>
     </row>
     <row r="224" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H224" s="40"/>
-      <c r="I224" s="40"/>
+      <c r="H224" s="38"/>
+      <c r="I224" s="38"/>
       <c r="J224" s="2"/>
       <c r="K224" s="2"/>
     </row>
     <row r="225" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H225" s="40"/>
-      <c r="I225" s="40"/>
+      <c r="H225" s="38"/>
+      <c r="I225" s="38"/>
       <c r="J225" s="2"/>
       <c r="K225" s="2"/>
     </row>
     <row r="226" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H226" s="40"/>
-      <c r="I226" s="40"/>
+      <c r="H226" s="38"/>
+      <c r="I226" s="38"/>
       <c r="J226" s="2"/>
       <c r="K226" s="2"/>
     </row>
     <row r="227" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H227" s="40"/>
-      <c r="I227" s="40"/>
+      <c r="H227" s="38"/>
+      <c r="I227" s="38"/>
       <c r="J227" s="2"/>
       <c r="K227" s="2"/>
     </row>
     <row r="228" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H228" s="40"/>
-      <c r="I228" s="40"/>
+      <c r="H228" s="38"/>
+      <c r="I228" s="38"/>
       <c r="J228" s="2"/>
       <c r="K228" s="2"/>
     </row>
     <row r="229" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H229" s="40"/>
-      <c r="I229" s="40"/>
+      <c r="H229" s="38"/>
+      <c r="I229" s="38"/>
       <c r="J229" s="2"/>
       <c r="K229" s="2"/>
     </row>
     <row r="230" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H230" s="40"/>
-      <c r="I230" s="40"/>
+      <c r="H230" s="38"/>
+      <c r="I230" s="38"/>
       <c r="J230" s="2"/>
       <c r="K230" s="2"/>
     </row>
     <row r="231" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H231" s="40"/>
-      <c r="I231" s="40"/>
+      <c r="H231" s="38"/>
+      <c r="I231" s="38"/>
       <c r="J231" s="2"/>
       <c r="K231" s="2"/>
     </row>
     <row r="232" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H232" s="40"/>
-      <c r="I232" s="40"/>
+      <c r="H232" s="38"/>
+      <c r="I232" s="38"/>
       <c r="J232" s="2"/>
       <c r="K232" s="2"/>
     </row>
     <row r="233" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H233" s="40"/>
-      <c r="I233" s="40"/>
+      <c r="H233" s="38"/>
+      <c r="I233" s="38"/>
       <c r="J233" s="2"/>
       <c r="K233" s="2"/>
     </row>
     <row r="234" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H234" s="40"/>
-      <c r="I234" s="40"/>
+      <c r="H234" s="38"/>
+      <c r="I234" s="38"/>
       <c r="J234" s="2"/>
       <c r="K234" s="2"/>
     </row>
     <row r="235" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H235" s="40"/>
-      <c r="I235" s="40"/>
+      <c r="H235" s="38"/>
+      <c r="I235" s="38"/>
       <c r="J235" s="2"/>
       <c r="K235" s="2"/>
     </row>
     <row r="236" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H236" s="40"/>
-      <c r="I236" s="40"/>
+      <c r="H236" s="38"/>
+      <c r="I236" s="38"/>
       <c r="J236" s="2"/>
       <c r="K236" s="2"/>
     </row>
     <row r="237" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H237" s="40"/>
-      <c r="I237" s="40"/>
+      <c r="H237" s="38"/>
+      <c r="I237" s="38"/>
       <c r="J237" s="2"/>
       <c r="K237" s="2"/>
     </row>
     <row r="238" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H238" s="40"/>
-      <c r="I238" s="40"/>
+      <c r="H238" s="38"/>
+      <c r="I238" s="38"/>
       <c r="J238" s="2"/>
       <c r="K238" s="2"/>
     </row>
     <row r="239" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H239" s="40"/>
-      <c r="I239" s="40"/>
+      <c r="H239" s="38"/>
+      <c r="I239" s="38"/>
       <c r="J239" s="2"/>
       <c r="K239" s="2"/>
     </row>
     <row r="240" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H240" s="40"/>
-      <c r="I240" s="40"/>
+      <c r="H240" s="38"/>
+      <c r="I240" s="38"/>
       <c r="J240" s="2"/>
       <c r="K240" s="2"/>
     </row>
     <row r="241" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H241" s="40"/>
-      <c r="I241" s="40"/>
+      <c r="H241" s="38"/>
+      <c r="I241" s="38"/>
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
     </row>
     <row r="242" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H242" s="40"/>
-      <c r="I242" s="40"/>
+      <c r="H242" s="38"/>
+      <c r="I242" s="38"/>
       <c r="J242" s="2"/>
       <c r="K242" s="2"/>
     </row>
     <row r="243" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H243" s="40"/>
-      <c r="I243" s="40"/>
+      <c r="H243" s="38"/>
+      <c r="I243" s="38"/>
       <c r="J243" s="2"/>
       <c r="K243" s="2"/>
     </row>
     <row r="244" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H244" s="40"/>
-      <c r="I244" s="40"/>
+      <c r="H244" s="38"/>
+      <c r="I244" s="38"/>
       <c r="J244" s="2"/>
       <c r="K244" s="2"/>
     </row>
     <row r="245" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H245" s="40"/>
-      <c r="I245" s="40"/>
+      <c r="H245" s="38"/>
+      <c r="I245" s="38"/>
       <c r="J245" s="2"/>
       <c r="K245" s="2"/>
     </row>
     <row r="246" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H246" s="40"/>
-      <c r="I246" s="40"/>
+      <c r="H246" s="38"/>
+      <c r="I246" s="38"/>
       <c r="J246" s="2"/>
       <c r="K246" s="2"/>
     </row>
     <row r="247" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H247" s="40"/>
-      <c r="I247" s="40"/>
+      <c r="H247" s="38"/>
+      <c r="I247" s="38"/>
       <c r="J247" s="2"/>
       <c r="K247" s="2"/>
     </row>
     <row r="248" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H248" s="40"/>
-      <c r="I248" s="40"/>
+      <c r="H248" s="38"/>
+      <c r="I248" s="38"/>
       <c r="J248" s="2"/>
       <c r="K248" s="2"/>
     </row>
     <row r="249" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H249" s="40"/>
-      <c r="I249" s="40"/>
+      <c r="H249" s="38"/>
+      <c r="I249" s="38"/>
       <c r="J249" s="2"/>
       <c r="K249" s="2"/>
     </row>
     <row r="250" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H250" s="40"/>
-      <c r="I250" s="40"/>
+      <c r="H250" s="38"/>
+      <c r="I250" s="38"/>
       <c r="J250" s="2"/>
       <c r="K250" s="2"/>
     </row>
     <row r="251" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H251" s="40"/>
-      <c r="I251" s="40"/>
+      <c r="H251" s="38"/>
+      <c r="I251" s="38"/>
       <c r="J251" s="2"/>
       <c r="K251" s="2"/>
     </row>
     <row r="252" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H252" s="40"/>
-      <c r="I252" s="40"/>
+      <c r="H252" s="38"/>
+      <c r="I252" s="38"/>
       <c r="J252" s="2"/>
       <c r="K252" s="2"/>
     </row>
     <row r="253" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H253" s="40"/>
-      <c r="I253" s="40"/>
+      <c r="H253" s="38"/>
+      <c r="I253" s="38"/>
       <c r="J253" s="2"/>
       <c r="K253" s="2"/>
     </row>
     <row r="254" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H254" s="40"/>
-      <c r="I254" s="40"/>
+      <c r="H254" s="38"/>
+      <c r="I254" s="38"/>
       <c r="J254" s="2"/>
       <c r="K254" s="2"/>
     </row>
     <row r="255" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H255" s="40"/>
-      <c r="I255" s="40"/>
+      <c r="H255" s="38"/>
+      <c r="I255" s="38"/>
       <c r="J255" s="2"/>
       <c r="K255" s="2"/>
     </row>
     <row r="256" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H256" s="40"/>
-      <c r="I256" s="40"/>
+      <c r="H256" s="38"/>
+      <c r="I256" s="38"/>
       <c r="J256" s="2"/>
       <c r="K256" s="2"/>
     </row>
     <row r="257" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H257" s="40"/>
-      <c r="I257" s="40"/>
+      <c r="H257" s="38"/>
+      <c r="I257" s="38"/>
       <c r="J257" s="2"/>
       <c r="K257" s="2"/>
     </row>
     <row r="258" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H258" s="40"/>
-      <c r="I258" s="40"/>
+      <c r="H258" s="38"/>
+      <c r="I258" s="38"/>
       <c r="J258" s="2"/>
       <c r="K258" s="2"/>
     </row>
     <row r="259" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H259" s="40"/>
-      <c r="I259" s="40"/>
+      <c r="H259" s="38"/>
+      <c r="I259" s="38"/>
       <c r="J259" s="2"/>
       <c r="K259" s="2"/>
     </row>
     <row r="260" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H260" s="40"/>
-      <c r="I260" s="40"/>
+      <c r="H260" s="38"/>
+      <c r="I260" s="38"/>
       <c r="J260" s="2"/>
       <c r="K260" s="2"/>
     </row>
     <row r="261" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H261" s="40"/>
-      <c r="I261" s="40"/>
+      <c r="H261" s="38"/>
+      <c r="I261" s="38"/>
       <c r="J261" s="2"/>
       <c r="K261" s="2"/>
     </row>
     <row r="262" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H262" s="40"/>
-      <c r="I262" s="40"/>
+      <c r="H262" s="38"/>
+      <c r="I262" s="38"/>
       <c r="J262" s="2"/>
       <c r="K262" s="2"/>
     </row>
     <row r="263" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H263" s="40"/>
-      <c r="I263" s="40"/>
+      <c r="H263" s="38"/>
+      <c r="I263" s="38"/>
       <c r="J263" s="2"/>
       <c r="K263" s="2"/>
     </row>
     <row r="264" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H264" s="40"/>
-      <c r="I264" s="40"/>
+      <c r="H264" s="38"/>
+      <c r="I264" s="38"/>
       <c r="J264" s="2"/>
       <c r="K264" s="2"/>
     </row>
     <row r="265" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H265" s="40"/>
-      <c r="I265" s="40"/>
+      <c r="H265" s="38"/>
+      <c r="I265" s="38"/>
       <c r="J265" s="2"/>
       <c r="K265" s="2"/>
     </row>
     <row r="266" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H266" s="40"/>
-      <c r="I266" s="40"/>
+      <c r="H266" s="38"/>
+      <c r="I266" s="38"/>
       <c r="J266" s="2"/>
       <c r="K266" s="2"/>
     </row>
     <row r="267" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H267" s="40"/>
-      <c r="I267" s="40"/>
+      <c r="H267" s="38"/>
+      <c r="I267" s="38"/>
       <c r="J267" s="2"/>
       <c r="K267" s="2"/>
     </row>
@@ -5211,464 +5248,464 @@
       <c r="J393" s="2"/>
     </row>
     <row r="394" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H394" s="40"/>
-      <c r="I394" s="40"/>
+      <c r="H394" s="38"/>
+      <c r="I394" s="38"/>
       <c r="J394" s="2"/>
       <c r="K394" s="2"/>
     </row>
     <row r="395" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H395" s="40"/>
-      <c r="I395" s="40"/>
+      <c r="H395" s="38"/>
+      <c r="I395" s="38"/>
       <c r="J395" s="2"/>
       <c r="K395" s="2"/>
     </row>
     <row r="396" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H396" s="40"/>
-      <c r="I396" s="40"/>
+      <c r="H396" s="38"/>
+      <c r="I396" s="38"/>
       <c r="J396" s="2"/>
       <c r="K396" s="2"/>
     </row>
     <row r="397" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H397" s="40"/>
-      <c r="I397" s="40"/>
+      <c r="H397" s="38"/>
+      <c r="I397" s="38"/>
       <c r="J397" s="2"/>
       <c r="K397" s="2"/>
     </row>
     <row r="398" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H398" s="40"/>
-      <c r="I398" s="40"/>
+      <c r="H398" s="38"/>
+      <c r="I398" s="38"/>
       <c r="J398" s="2"/>
       <c r="K398" s="2"/>
     </row>
     <row r="399" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H399" s="40"/>
-      <c r="I399" s="40"/>
+      <c r="H399" s="38"/>
+      <c r="I399" s="38"/>
       <c r="J399" s="2"/>
       <c r="K399" s="2"/>
     </row>
     <row r="400" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H400" s="40"/>
-      <c r="I400" s="40"/>
+      <c r="H400" s="38"/>
+      <c r="I400" s="38"/>
       <c r="J400" s="2"/>
       <c r="K400" s="2"/>
     </row>
     <row r="401" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H401" s="40"/>
-      <c r="I401" s="40"/>
+      <c r="H401" s="38"/>
+      <c r="I401" s="38"/>
       <c r="J401" s="2"/>
       <c r="K401" s="2"/>
     </row>
     <row r="402" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H402" s="40"/>
-      <c r="I402" s="40"/>
+      <c r="H402" s="38"/>
+      <c r="I402" s="38"/>
       <c r="J402" s="2"/>
       <c r="K402" s="2"/>
     </row>
     <row r="403" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H403" s="40"/>
-      <c r="I403" s="40"/>
+      <c r="H403" s="38"/>
+      <c r="I403" s="38"/>
       <c r="J403" s="2"/>
       <c r="K403" s="2"/>
     </row>
     <row r="404" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H404" s="40"/>
-      <c r="I404" s="40"/>
+      <c r="H404" s="38"/>
+      <c r="I404" s="38"/>
       <c r="J404" s="2"/>
       <c r="K404" s="2"/>
     </row>
     <row r="405" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H405" s="40"/>
-      <c r="I405" s="40"/>
+      <c r="H405" s="38"/>
+      <c r="I405" s="38"/>
       <c r="J405" s="2"/>
       <c r="K405" s="2"/>
     </row>
     <row r="406" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H406" s="40"/>
-      <c r="I406" s="40"/>
+      <c r="H406" s="38"/>
+      <c r="I406" s="38"/>
       <c r="J406" s="2"/>
       <c r="K406" s="2"/>
     </row>
     <row r="407" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H407" s="40"/>
-      <c r="I407" s="40"/>
+      <c r="H407" s="38"/>
+      <c r="I407" s="38"/>
       <c r="J407" s="2"/>
       <c r="K407" s="2"/>
     </row>
     <row r="408" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H408" s="40"/>
-      <c r="I408" s="40"/>
+      <c r="H408" s="38"/>
+      <c r="I408" s="38"/>
       <c r="J408" s="2"/>
       <c r="K408" s="2"/>
     </row>
     <row r="409" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H409" s="40"/>
-      <c r="I409" s="40"/>
+      <c r="H409" s="38"/>
+      <c r="I409" s="38"/>
       <c r="J409" s="2"/>
       <c r="K409" s="2"/>
     </row>
     <row r="410" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H410" s="40"/>
-      <c r="I410" s="40"/>
+      <c r="H410" s="38"/>
+      <c r="I410" s="38"/>
       <c r="J410" s="2"/>
       <c r="K410" s="2"/>
     </row>
     <row r="411" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H411" s="40"/>
-      <c r="I411" s="40"/>
+      <c r="H411" s="38"/>
+      <c r="I411" s="38"/>
       <c r="J411" s="2"/>
       <c r="K411" s="2"/>
     </row>
     <row r="412" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H412" s="40"/>
-      <c r="I412" s="40"/>
+      <c r="H412" s="38"/>
+      <c r="I412" s="38"/>
       <c r="J412" s="2"/>
       <c r="K412" s="2"/>
     </row>
     <row r="413" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H413" s="40"/>
-      <c r="I413" s="40"/>
+      <c r="H413" s="38"/>
+      <c r="I413" s="38"/>
       <c r="J413" s="2"/>
       <c r="K413" s="2"/>
     </row>
     <row r="414" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H414" s="40"/>
-      <c r="I414" s="40"/>
+      <c r="H414" s="38"/>
+      <c r="I414" s="38"/>
       <c r="J414" s="2"/>
       <c r="K414" s="2"/>
     </row>
     <row r="415" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H415" s="40"/>
-      <c r="I415" s="40"/>
+      <c r="H415" s="38"/>
+      <c r="I415" s="38"/>
       <c r="J415" s="2"/>
       <c r="K415" s="2"/>
     </row>
     <row r="416" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H416" s="40"/>
-      <c r="I416" s="40"/>
+      <c r="H416" s="38"/>
+      <c r="I416" s="38"/>
       <c r="J416" s="2"/>
       <c r="K416" s="2"/>
     </row>
     <row r="417" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H417" s="40"/>
-      <c r="I417" s="40"/>
+      <c r="H417" s="38"/>
+      <c r="I417" s="38"/>
       <c r="J417" s="2"/>
       <c r="K417" s="2"/>
     </row>
     <row r="418" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H418" s="40"/>
-      <c r="I418" s="40"/>
+      <c r="H418" s="38"/>
+      <c r="I418" s="38"/>
       <c r="J418" s="2"/>
       <c r="K418" s="2"/>
     </row>
     <row r="419" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H419" s="40"/>
-      <c r="I419" s="40"/>
+      <c r="H419" s="38"/>
+      <c r="I419" s="38"/>
       <c r="J419" s="2"/>
       <c r="K419" s="2"/>
     </row>
     <row r="420" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H420" s="40"/>
-      <c r="I420" s="40"/>
+      <c r="H420" s="38"/>
+      <c r="I420" s="38"/>
       <c r="J420" s="2"/>
       <c r="K420" s="2"/>
     </row>
     <row r="421" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H421" s="40"/>
-      <c r="I421" s="40"/>
+      <c r="H421" s="38"/>
+      <c r="I421" s="38"/>
       <c r="J421" s="2"/>
       <c r="K421" s="2"/>
     </row>
     <row r="422" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H422" s="40"/>
-      <c r="I422" s="40"/>
+      <c r="H422" s="38"/>
+      <c r="I422" s="38"/>
       <c r="J422" s="2"/>
       <c r="K422" s="2"/>
     </row>
     <row r="423" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H423" s="40"/>
-      <c r="I423" s="40"/>
+      <c r="H423" s="38"/>
+      <c r="I423" s="38"/>
       <c r="J423" s="2"/>
       <c r="K423" s="2"/>
     </row>
     <row r="424" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H424" s="40"/>
-      <c r="I424" s="40"/>
+      <c r="H424" s="38"/>
+      <c r="I424" s="38"/>
       <c r="J424" s="2"/>
       <c r="K424" s="2"/>
     </row>
     <row r="425" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H425" s="40"/>
-      <c r="I425" s="40"/>
+      <c r="H425" s="38"/>
+      <c r="I425" s="38"/>
       <c r="J425" s="2"/>
       <c r="K425" s="2"/>
     </row>
     <row r="426" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H426" s="40"/>
-      <c r="I426" s="40"/>
+      <c r="H426" s="38"/>
+      <c r="I426" s="38"/>
       <c r="J426" s="2"/>
       <c r="K426" s="2"/>
     </row>
     <row r="427" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H427" s="40"/>
-      <c r="I427" s="40"/>
+      <c r="H427" s="38"/>
+      <c r="I427" s="38"/>
       <c r="J427" s="2"/>
       <c r="K427" s="2"/>
     </row>
     <row r="428" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H428" s="40"/>
-      <c r="I428" s="40"/>
+      <c r="H428" s="38"/>
+      <c r="I428" s="38"/>
       <c r="J428" s="2"/>
       <c r="K428" s="2"/>
     </row>
     <row r="429" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H429" s="40"/>
-      <c r="I429" s="40"/>
+      <c r="H429" s="38"/>
+      <c r="I429" s="38"/>
       <c r="J429" s="2"/>
       <c r="K429" s="2"/>
     </row>
     <row r="430" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H430" s="40"/>
-      <c r="I430" s="40"/>
+      <c r="H430" s="38"/>
+      <c r="I430" s="38"/>
       <c r="J430" s="2"/>
       <c r="K430" s="2"/>
     </row>
     <row r="431" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H431" s="40"/>
-      <c r="I431" s="40"/>
+      <c r="H431" s="38"/>
+      <c r="I431" s="38"/>
       <c r="J431" s="2"/>
       <c r="K431" s="2"/>
     </row>
     <row r="432" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H432" s="40"/>
-      <c r="I432" s="40"/>
+      <c r="H432" s="38"/>
+      <c r="I432" s="38"/>
       <c r="J432" s="2"/>
       <c r="K432" s="2"/>
     </row>
     <row r="433" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H433" s="40"/>
-      <c r="I433" s="40"/>
+      <c r="H433" s="38"/>
+      <c r="I433" s="38"/>
       <c r="J433" s="2"/>
       <c r="K433" s="2"/>
     </row>
     <row r="434" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H434" s="40"/>
-      <c r="I434" s="40"/>
+      <c r="H434" s="38"/>
+      <c r="I434" s="38"/>
       <c r="J434" s="2"/>
       <c r="K434" s="2"/>
     </row>
     <row r="435" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H435" s="40"/>
-      <c r="I435" s="40"/>
+      <c r="H435" s="38"/>
+      <c r="I435" s="38"/>
       <c r="J435" s="2"/>
       <c r="K435" s="2"/>
     </row>
     <row r="436" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H436" s="40"/>
-      <c r="I436" s="40"/>
+      <c r="H436" s="38"/>
+      <c r="I436" s="38"/>
       <c r="J436" s="2"/>
       <c r="K436" s="2"/>
     </row>
     <row r="437" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H437" s="40"/>
-      <c r="I437" s="40"/>
+      <c r="H437" s="38"/>
+      <c r="I437" s="38"/>
       <c r="J437" s="2"/>
       <c r="K437" s="2"/>
     </row>
     <row r="438" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H438" s="40"/>
-      <c r="I438" s="40"/>
+      <c r="H438" s="38"/>
+      <c r="I438" s="38"/>
       <c r="J438" s="2"/>
       <c r="K438" s="2"/>
     </row>
     <row r="439" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H439" s="40"/>
-      <c r="I439" s="40"/>
+      <c r="H439" s="38"/>
+      <c r="I439" s="38"/>
       <c r="J439" s="2"/>
       <c r="K439" s="2"/>
     </row>
     <row r="440" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H440" s="40"/>
-      <c r="I440" s="40"/>
+      <c r="H440" s="38"/>
+      <c r="I440" s="38"/>
       <c r="J440" s="2"/>
       <c r="K440" s="2"/>
     </row>
     <row r="441" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H441" s="40"/>
-      <c r="I441" s="40"/>
+      <c r="H441" s="38"/>
+      <c r="I441" s="38"/>
       <c r="J441" s="2"/>
       <c r="K441" s="2"/>
     </row>
     <row r="442" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H442" s="40"/>
-      <c r="I442" s="40"/>
+      <c r="H442" s="38"/>
+      <c r="I442" s="38"/>
       <c r="J442" s="2"/>
       <c r="K442" s="2"/>
     </row>
     <row r="443" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H443" s="40"/>
-      <c r="I443" s="40"/>
+      <c r="H443" s="38"/>
+      <c r="I443" s="38"/>
       <c r="J443" s="2"/>
       <c r="K443" s="2"/>
     </row>
     <row r="444" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H444" s="40"/>
-      <c r="I444" s="40"/>
+      <c r="H444" s="38"/>
+      <c r="I444" s="38"/>
       <c r="J444" s="2"/>
       <c r="K444" s="2"/>
     </row>
     <row r="445" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H445" s="40"/>
-      <c r="I445" s="40"/>
+      <c r="H445" s="38"/>
+      <c r="I445" s="38"/>
       <c r="J445" s="2"/>
       <c r="K445" s="2"/>
     </row>
     <row r="446" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H446" s="40"/>
-      <c r="I446" s="40"/>
+      <c r="H446" s="38"/>
+      <c r="I446" s="38"/>
       <c r="J446" s="2"/>
       <c r="K446" s="2"/>
     </row>
     <row r="447" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H447" s="40"/>
-      <c r="I447" s="40"/>
+      <c r="H447" s="38"/>
+      <c r="I447" s="38"/>
       <c r="J447" s="2"/>
       <c r="K447" s="2"/>
     </row>
     <row r="448" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H448" s="40"/>
-      <c r="I448" s="40"/>
+      <c r="H448" s="38"/>
+      <c r="I448" s="38"/>
       <c r="J448" s="2"/>
       <c r="K448" s="2"/>
     </row>
     <row r="449" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H449" s="40"/>
-      <c r="I449" s="40"/>
+      <c r="H449" s="38"/>
+      <c r="I449" s="38"/>
       <c r="J449" s="2"/>
       <c r="K449" s="2"/>
     </row>
     <row r="450" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H450" s="40"/>
-      <c r="I450" s="40"/>
+      <c r="H450" s="38"/>
+      <c r="I450" s="38"/>
       <c r="J450" s="2"/>
       <c r="K450" s="2"/>
     </row>
     <row r="451" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H451" s="40"/>
-      <c r="I451" s="40"/>
+      <c r="H451" s="38"/>
+      <c r="I451" s="38"/>
       <c r="J451" s="2"/>
       <c r="K451" s="2"/>
     </row>
     <row r="452" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H452" s="40"/>
-      <c r="I452" s="40"/>
+      <c r="H452" s="38"/>
+      <c r="I452" s="38"/>
       <c r="J452" s="2"/>
       <c r="K452" s="2"/>
     </row>
     <row r="453" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H453" s="40"/>
-      <c r="I453" s="40"/>
+      <c r="H453" s="38"/>
+      <c r="I453" s="38"/>
       <c r="J453" s="2"/>
       <c r="K453" s="2"/>
     </row>
     <row r="454" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H454" s="40"/>
-      <c r="I454" s="40"/>
+      <c r="H454" s="38"/>
+      <c r="I454" s="38"/>
       <c r="J454" s="2"/>
       <c r="K454" s="2"/>
     </row>
     <row r="455" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H455" s="40"/>
-      <c r="I455" s="40"/>
+      <c r="H455" s="38"/>
+      <c r="I455" s="38"/>
       <c r="J455" s="2"/>
       <c r="K455" s="2"/>
     </row>
     <row r="456" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H456" s="40"/>
-      <c r="I456" s="40"/>
+      <c r="H456" s="38"/>
+      <c r="I456" s="38"/>
       <c r="J456" s="2"/>
       <c r="K456" s="2"/>
     </row>
     <row r="457" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H457" s="40"/>
-      <c r="I457" s="40"/>
+      <c r="H457" s="38"/>
+      <c r="I457" s="38"/>
       <c r="J457" s="2"/>
       <c r="K457" s="2"/>
     </row>
     <row r="458" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H458" s="40"/>
-      <c r="I458" s="40"/>
+      <c r="H458" s="38"/>
+      <c r="I458" s="38"/>
       <c r="J458" s="2"/>
       <c r="K458" s="2"/>
     </row>
     <row r="459" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H459" s="40"/>
-      <c r="I459" s="40"/>
+      <c r="H459" s="38"/>
+      <c r="I459" s="38"/>
       <c r="J459" s="2"/>
       <c r="K459" s="2"/>
     </row>
     <row r="460" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H460" s="40"/>
-      <c r="I460" s="40"/>
+      <c r="H460" s="38"/>
+      <c r="I460" s="38"/>
       <c r="J460" s="2"/>
       <c r="K460" s="2"/>
     </row>
     <row r="461" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H461" s="40"/>
-      <c r="I461" s="40"/>
+      <c r="H461" s="38"/>
+      <c r="I461" s="38"/>
       <c r="J461" s="2"/>
       <c r="K461" s="2"/>
     </row>
     <row r="462" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H462" s="40"/>
-      <c r="I462" s="40"/>
+      <c r="H462" s="38"/>
+      <c r="I462" s="38"/>
       <c r="J462" s="2"/>
       <c r="K462" s="2"/>
     </row>
     <row r="463" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H463" s="40"/>
-      <c r="I463" s="40"/>
+      <c r="H463" s="38"/>
+      <c r="I463" s="38"/>
       <c r="J463" s="2"/>
       <c r="K463" s="2"/>
     </row>
     <row r="464" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H464" s="40"/>
-      <c r="I464" s="40"/>
+      <c r="H464" s="38"/>
+      <c r="I464" s="38"/>
       <c r="J464" s="2"/>
       <c r="K464" s="2"/>
     </row>
     <row r="465" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H465" s="40"/>
-      <c r="I465" s="40"/>
+      <c r="H465" s="38"/>
+      <c r="I465" s="38"/>
       <c r="J465" s="2"/>
       <c r="K465" s="2"/>
     </row>
     <row r="466" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H466" s="40"/>
-      <c r="I466" s="40"/>
+      <c r="H466" s="38"/>
+      <c r="I466" s="38"/>
       <c r="J466" s="2"/>
       <c r="K466" s="2"/>
     </row>
     <row r="467" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H467" s="40"/>
-      <c r="I467" s="40"/>
+      <c r="H467" s="38"/>
+      <c r="I467" s="38"/>
       <c r="J467" s="2"/>
       <c r="K467" s="2"/>
     </row>
     <row r="468" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H468" s="40"/>
-      <c r="I468" s="40"/>
+      <c r="H468" s="38"/>
+      <c r="I468" s="38"/>
       <c r="J468" s="2"/>
       <c r="K468" s="2"/>
     </row>
     <row r="469" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H469" s="40"/>
-      <c r="I469" s="40"/>
+      <c r="H469" s="38"/>
+      <c r="I469" s="38"/>
       <c r="J469" s="2"/>
       <c r="K469" s="2"/>
     </row>
     <row r="470" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H470" s="40"/>
-      <c r="I470" s="40"/>
+      <c r="H470" s="38"/>
+      <c r="I470" s="38"/>
       <c r="J470" s="2"/>
       <c r="K470" s="2"/>
     </row>
@@ -6054,92 +6091,92 @@
       <c r="J597" s="2"/>
     </row>
     <row r="598" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H598" s="40"/>
-      <c r="I598" s="40"/>
+      <c r="H598" s="38"/>
+      <c r="I598" s="38"/>
       <c r="J598" s="2"/>
       <c r="K598" s="2"/>
     </row>
     <row r="599" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H599" s="40"/>
-      <c r="I599" s="40"/>
+      <c r="H599" s="38"/>
+      <c r="I599" s="38"/>
       <c r="J599" s="2"/>
       <c r="K599" s="2"/>
     </row>
     <row r="600" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H600" s="40"/>
-      <c r="I600" s="40"/>
+      <c r="H600" s="38"/>
+      <c r="I600" s="38"/>
       <c r="J600" s="2"/>
       <c r="K600" s="2"/>
     </row>
     <row r="601" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H601" s="40"/>
-      <c r="I601" s="40"/>
+      <c r="H601" s="38"/>
+      <c r="I601" s="38"/>
       <c r="J601" s="2"/>
       <c r="K601" s="2"/>
     </row>
     <row r="602" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H602" s="40"/>
-      <c r="I602" s="40"/>
+      <c r="H602" s="38"/>
+      <c r="I602" s="38"/>
       <c r="J602" s="2"/>
       <c r="K602" s="2"/>
     </row>
     <row r="603" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H603" s="40"/>
-      <c r="I603" s="40"/>
+      <c r="H603" s="38"/>
+      <c r="I603" s="38"/>
       <c r="J603" s="2"/>
       <c r="K603" s="2"/>
     </row>
     <row r="604" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H604" s="40"/>
-      <c r="I604" s="40"/>
+      <c r="H604" s="38"/>
+      <c r="I604" s="38"/>
       <c r="J604" s="2"/>
       <c r="K604" s="2"/>
     </row>
     <row r="605" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H605" s="40"/>
-      <c r="I605" s="40"/>
+      <c r="H605" s="38"/>
+      <c r="I605" s="38"/>
       <c r="J605" s="2"/>
       <c r="K605" s="2"/>
     </row>
     <row r="606" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H606" s="40"/>
-      <c r="I606" s="40"/>
+      <c r="H606" s="38"/>
+      <c r="I606" s="38"/>
       <c r="J606" s="2"/>
       <c r="K606" s="2"/>
     </row>
     <row r="607" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H607" s="40"/>
-      <c r="I607" s="40"/>
+      <c r="H607" s="38"/>
+      <c r="I607" s="38"/>
       <c r="J607" s="2"/>
       <c r="K607" s="2"/>
     </row>
     <row r="608" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H608" s="40"/>
-      <c r="I608" s="40"/>
+      <c r="H608" s="38"/>
+      <c r="I608" s="38"/>
       <c r="J608" s="2"/>
       <c r="K608" s="2"/>
     </row>
     <row r="609" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H609" s="40"/>
-      <c r="I609" s="40"/>
+      <c r="H609" s="38"/>
+      <c r="I609" s="38"/>
       <c r="J609" s="2"/>
       <c r="K609" s="2"/>
     </row>
     <row r="610" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H610" s="40"/>
-      <c r="I610" s="40"/>
+      <c r="H610" s="38"/>
+      <c r="I610" s="38"/>
       <c r="J610" s="2"/>
       <c r="K610" s="2"/>
     </row>
     <row r="611" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H611" s="40"/>
-      <c r="I611" s="40"/>
+      <c r="H611" s="38"/>
+      <c r="I611" s="38"/>
       <c r="J611" s="2"/>
       <c r="K611" s="2"/>
     </row>
     <row r="612" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H612" s="40"/>
-      <c r="I612" s="40"/>
+      <c r="H612" s="38"/>
+      <c r="I612" s="38"/>
       <c r="J612" s="2"/>
       <c r="K612" s="2"/>
     </row>
@@ -6157,100 +6194,66 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.1640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.1640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.83203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="12.83203125" style="54"/>
+    <col min="1" max="1" width="7.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="12.83203125" style="52"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="61" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>53</v>
+      <c r="E1" s="57" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>113</v>
+      <c r="A2" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>113</v>
+      <c r="B3" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6277,131 +6280,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="41"/>
+      <c r="E1" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="67" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="A2" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="68" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="A3" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="68" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
+      <c r="A4" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="67" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="67" t="s">
+      <c r="A5" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
+      <c r="C5" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="67" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>116</v>
-      </c>
-      <c r="E6" s="69" t="s">
-        <v>128</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
+      <c r="A6" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
@@ -6514,464 +6517,464 @@
       <c r="J190" s="2"/>
     </row>
     <row r="191" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H191" s="40"/>
-      <c r="I191" s="40"/>
+      <c r="H191" s="38"/>
+      <c r="I191" s="38"/>
       <c r="J191" s="2"/>
       <c r="K191" s="2"/>
     </row>
     <row r="192" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H192" s="40"/>
-      <c r="I192" s="40"/>
+      <c r="H192" s="38"/>
+      <c r="I192" s="38"/>
       <c r="J192" s="2"/>
       <c r="K192" s="2"/>
     </row>
     <row r="193" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H193" s="40"/>
-      <c r="I193" s="40"/>
+      <c r="H193" s="38"/>
+      <c r="I193" s="38"/>
       <c r="J193" s="2"/>
       <c r="K193" s="2"/>
     </row>
     <row r="194" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H194" s="40"/>
-      <c r="I194" s="40"/>
+      <c r="H194" s="38"/>
+      <c r="I194" s="38"/>
       <c r="J194" s="2"/>
       <c r="K194" s="2"/>
     </row>
     <row r="195" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H195" s="40"/>
-      <c r="I195" s="40"/>
+      <c r="H195" s="38"/>
+      <c r="I195" s="38"/>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
     </row>
     <row r="196" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H196" s="40"/>
-      <c r="I196" s="40"/>
+      <c r="H196" s="38"/>
+      <c r="I196" s="38"/>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
     </row>
     <row r="197" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H197" s="40"/>
-      <c r="I197" s="40"/>
+      <c r="H197" s="38"/>
+      <c r="I197" s="38"/>
       <c r="J197" s="2"/>
       <c r="K197" s="2"/>
     </row>
     <row r="198" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H198" s="40"/>
-      <c r="I198" s="40"/>
+      <c r="H198" s="38"/>
+      <c r="I198" s="38"/>
       <c r="J198" s="2"/>
       <c r="K198" s="2"/>
     </row>
     <row r="199" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H199" s="40"/>
-      <c r="I199" s="40"/>
+      <c r="H199" s="38"/>
+      <c r="I199" s="38"/>
       <c r="J199" s="2"/>
       <c r="K199" s="2"/>
     </row>
     <row r="200" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H200" s="40"/>
-      <c r="I200" s="40"/>
+      <c r="H200" s="38"/>
+      <c r="I200" s="38"/>
       <c r="J200" s="2"/>
       <c r="K200" s="2"/>
     </row>
     <row r="201" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H201" s="40"/>
-      <c r="I201" s="40"/>
+      <c r="H201" s="38"/>
+      <c r="I201" s="38"/>
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
     </row>
     <row r="202" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H202" s="40"/>
-      <c r="I202" s="40"/>
+      <c r="H202" s="38"/>
+      <c r="I202" s="38"/>
       <c r="J202" s="2"/>
       <c r="K202" s="2"/>
     </row>
     <row r="203" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H203" s="40"/>
-      <c r="I203" s="40"/>
+      <c r="H203" s="38"/>
+      <c r="I203" s="38"/>
       <c r="J203" s="2"/>
       <c r="K203" s="2"/>
     </row>
     <row r="204" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H204" s="40"/>
-      <c r="I204" s="40"/>
+      <c r="H204" s="38"/>
+      <c r="I204" s="38"/>
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
     </row>
     <row r="205" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H205" s="40"/>
-      <c r="I205" s="40"/>
+      <c r="H205" s="38"/>
+      <c r="I205" s="38"/>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
     </row>
     <row r="206" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H206" s="40"/>
-      <c r="I206" s="40"/>
+      <c r="H206" s="38"/>
+      <c r="I206" s="38"/>
       <c r="J206" s="2"/>
       <c r="K206" s="2"/>
     </row>
     <row r="207" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H207" s="40"/>
-      <c r="I207" s="40"/>
+      <c r="H207" s="38"/>
+      <c r="I207" s="38"/>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
     </row>
     <row r="208" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H208" s="40"/>
-      <c r="I208" s="40"/>
+      <c r="H208" s="38"/>
+      <c r="I208" s="38"/>
       <c r="J208" s="2"/>
       <c r="K208" s="2"/>
     </row>
     <row r="209" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H209" s="40"/>
-      <c r="I209" s="40"/>
+      <c r="H209" s="38"/>
+      <c r="I209" s="38"/>
       <c r="J209" s="2"/>
       <c r="K209" s="2"/>
     </row>
     <row r="210" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H210" s="40"/>
-      <c r="I210" s="40"/>
+      <c r="H210" s="38"/>
+      <c r="I210" s="38"/>
       <c r="J210" s="2"/>
       <c r="K210" s="2"/>
     </row>
     <row r="211" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H211" s="40"/>
-      <c r="I211" s="40"/>
+      <c r="H211" s="38"/>
+      <c r="I211" s="38"/>
       <c r="J211" s="2"/>
       <c r="K211" s="2"/>
     </row>
     <row r="212" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H212" s="40"/>
-      <c r="I212" s="40"/>
+      <c r="H212" s="38"/>
+      <c r="I212" s="38"/>
       <c r="J212" s="2"/>
       <c r="K212" s="2"/>
     </row>
     <row r="213" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H213" s="40"/>
-      <c r="I213" s="40"/>
+      <c r="H213" s="38"/>
+      <c r="I213" s="38"/>
       <c r="J213" s="2"/>
       <c r="K213" s="2"/>
     </row>
     <row r="214" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H214" s="40"/>
-      <c r="I214" s="40"/>
+      <c r="H214" s="38"/>
+      <c r="I214" s="38"/>
       <c r="J214" s="2"/>
       <c r="K214" s="2"/>
     </row>
     <row r="215" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H215" s="40"/>
-      <c r="I215" s="40"/>
+      <c r="H215" s="38"/>
+      <c r="I215" s="38"/>
       <c r="J215" s="2"/>
       <c r="K215" s="2"/>
     </row>
     <row r="216" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H216" s="40"/>
-      <c r="I216" s="40"/>
+      <c r="H216" s="38"/>
+      <c r="I216" s="38"/>
       <c r="J216" s="2"/>
       <c r="K216" s="2"/>
     </row>
     <row r="217" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H217" s="40"/>
-      <c r="I217" s="40"/>
+      <c r="H217" s="38"/>
+      <c r="I217" s="38"/>
       <c r="J217" s="2"/>
       <c r="K217" s="2"/>
     </row>
     <row r="218" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H218" s="40"/>
-      <c r="I218" s="40"/>
+      <c r="H218" s="38"/>
+      <c r="I218" s="38"/>
       <c r="J218" s="2"/>
       <c r="K218" s="2"/>
     </row>
     <row r="219" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H219" s="40"/>
-      <c r="I219" s="40"/>
+      <c r="H219" s="38"/>
+      <c r="I219" s="38"/>
       <c r="J219" s="2"/>
       <c r="K219" s="2"/>
     </row>
     <row r="220" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H220" s="40"/>
-      <c r="I220" s="40"/>
+      <c r="H220" s="38"/>
+      <c r="I220" s="38"/>
       <c r="J220" s="2"/>
       <c r="K220" s="2"/>
     </row>
     <row r="221" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H221" s="40"/>
-      <c r="I221" s="40"/>
+      <c r="H221" s="38"/>
+      <c r="I221" s="38"/>
       <c r="J221" s="2"/>
       <c r="K221" s="2"/>
     </row>
     <row r="222" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H222" s="40"/>
-      <c r="I222" s="40"/>
+      <c r="H222" s="38"/>
+      <c r="I222" s="38"/>
       <c r="J222" s="2"/>
       <c r="K222" s="2"/>
     </row>
     <row r="223" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H223" s="40"/>
-      <c r="I223" s="40"/>
+      <c r="H223" s="38"/>
+      <c r="I223" s="38"/>
       <c r="J223" s="2"/>
       <c r="K223" s="2"/>
     </row>
     <row r="224" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H224" s="40"/>
-      <c r="I224" s="40"/>
+      <c r="H224" s="38"/>
+      <c r="I224" s="38"/>
       <c r="J224" s="2"/>
       <c r="K224" s="2"/>
     </row>
     <row r="225" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H225" s="40"/>
-      <c r="I225" s="40"/>
+      <c r="H225" s="38"/>
+      <c r="I225" s="38"/>
       <c r="J225" s="2"/>
       <c r="K225" s="2"/>
     </row>
     <row r="226" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H226" s="40"/>
-      <c r="I226" s="40"/>
+      <c r="H226" s="38"/>
+      <c r="I226" s="38"/>
       <c r="J226" s="2"/>
       <c r="K226" s="2"/>
     </row>
     <row r="227" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H227" s="40"/>
-      <c r="I227" s="40"/>
+      <c r="H227" s="38"/>
+      <c r="I227" s="38"/>
       <c r="J227" s="2"/>
       <c r="K227" s="2"/>
     </row>
     <row r="228" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H228" s="40"/>
-      <c r="I228" s="40"/>
+      <c r="H228" s="38"/>
+      <c r="I228" s="38"/>
       <c r="J228" s="2"/>
       <c r="K228" s="2"/>
     </row>
     <row r="229" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H229" s="40"/>
-      <c r="I229" s="40"/>
+      <c r="H229" s="38"/>
+      <c r="I229" s="38"/>
       <c r="J229" s="2"/>
       <c r="K229" s="2"/>
     </row>
     <row r="230" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H230" s="40"/>
-      <c r="I230" s="40"/>
+      <c r="H230" s="38"/>
+      <c r="I230" s="38"/>
       <c r="J230" s="2"/>
       <c r="K230" s="2"/>
     </row>
     <row r="231" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H231" s="40"/>
-      <c r="I231" s="40"/>
+      <c r="H231" s="38"/>
+      <c r="I231" s="38"/>
       <c r="J231" s="2"/>
       <c r="K231" s="2"/>
     </row>
     <row r="232" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H232" s="40"/>
-      <c r="I232" s="40"/>
+      <c r="H232" s="38"/>
+      <c r="I232" s="38"/>
       <c r="J232" s="2"/>
       <c r="K232" s="2"/>
     </row>
     <row r="233" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H233" s="40"/>
-      <c r="I233" s="40"/>
+      <c r="H233" s="38"/>
+      <c r="I233" s="38"/>
       <c r="J233" s="2"/>
       <c r="K233" s="2"/>
     </row>
     <row r="234" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H234" s="40"/>
-      <c r="I234" s="40"/>
+      <c r="H234" s="38"/>
+      <c r="I234" s="38"/>
       <c r="J234" s="2"/>
       <c r="K234" s="2"/>
     </row>
     <row r="235" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H235" s="40"/>
-      <c r="I235" s="40"/>
+      <c r="H235" s="38"/>
+      <c r="I235" s="38"/>
       <c r="J235" s="2"/>
       <c r="K235" s="2"/>
     </row>
     <row r="236" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H236" s="40"/>
-      <c r="I236" s="40"/>
+      <c r="H236" s="38"/>
+      <c r="I236" s="38"/>
       <c r="J236" s="2"/>
       <c r="K236" s="2"/>
     </row>
     <row r="237" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H237" s="40"/>
-      <c r="I237" s="40"/>
+      <c r="H237" s="38"/>
+      <c r="I237" s="38"/>
       <c r="J237" s="2"/>
       <c r="K237" s="2"/>
     </row>
     <row r="238" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H238" s="40"/>
-      <c r="I238" s="40"/>
+      <c r="H238" s="38"/>
+      <c r="I238" s="38"/>
       <c r="J238" s="2"/>
       <c r="K238" s="2"/>
     </row>
     <row r="239" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H239" s="40"/>
-      <c r="I239" s="40"/>
+      <c r="H239" s="38"/>
+      <c r="I239" s="38"/>
       <c r="J239" s="2"/>
       <c r="K239" s="2"/>
     </row>
     <row r="240" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H240" s="40"/>
-      <c r="I240" s="40"/>
+      <c r="H240" s="38"/>
+      <c r="I240" s="38"/>
       <c r="J240" s="2"/>
       <c r="K240" s="2"/>
     </row>
     <row r="241" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H241" s="40"/>
-      <c r="I241" s="40"/>
+      <c r="H241" s="38"/>
+      <c r="I241" s="38"/>
       <c r="J241" s="2"/>
       <c r="K241" s="2"/>
     </row>
     <row r="242" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H242" s="40"/>
-      <c r="I242" s="40"/>
+      <c r="H242" s="38"/>
+      <c r="I242" s="38"/>
       <c r="J242" s="2"/>
       <c r="K242" s="2"/>
     </row>
     <row r="243" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H243" s="40"/>
-      <c r="I243" s="40"/>
+      <c r="H243" s="38"/>
+      <c r="I243" s="38"/>
       <c r="J243" s="2"/>
       <c r="K243" s="2"/>
     </row>
     <row r="244" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H244" s="40"/>
-      <c r="I244" s="40"/>
+      <c r="H244" s="38"/>
+      <c r="I244" s="38"/>
       <c r="J244" s="2"/>
       <c r="K244" s="2"/>
     </row>
     <row r="245" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H245" s="40"/>
-      <c r="I245" s="40"/>
+      <c r="H245" s="38"/>
+      <c r="I245" s="38"/>
       <c r="J245" s="2"/>
       <c r="K245" s="2"/>
     </row>
     <row r="246" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H246" s="40"/>
-      <c r="I246" s="40"/>
+      <c r="H246" s="38"/>
+      <c r="I246" s="38"/>
       <c r="J246" s="2"/>
       <c r="K246" s="2"/>
     </row>
     <row r="247" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H247" s="40"/>
-      <c r="I247" s="40"/>
+      <c r="H247" s="38"/>
+      <c r="I247" s="38"/>
       <c r="J247" s="2"/>
       <c r="K247" s="2"/>
     </row>
     <row r="248" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H248" s="40"/>
-      <c r="I248" s="40"/>
+      <c r="H248" s="38"/>
+      <c r="I248" s="38"/>
       <c r="J248" s="2"/>
       <c r="K248" s="2"/>
     </row>
     <row r="249" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H249" s="40"/>
-      <c r="I249" s="40"/>
+      <c r="H249" s="38"/>
+      <c r="I249" s="38"/>
       <c r="J249" s="2"/>
       <c r="K249" s="2"/>
     </row>
     <row r="250" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H250" s="40"/>
-      <c r="I250" s="40"/>
+      <c r="H250" s="38"/>
+      <c r="I250" s="38"/>
       <c r="J250" s="2"/>
       <c r="K250" s="2"/>
     </row>
     <row r="251" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H251" s="40"/>
-      <c r="I251" s="40"/>
+      <c r="H251" s="38"/>
+      <c r="I251" s="38"/>
       <c r="J251" s="2"/>
       <c r="K251" s="2"/>
     </row>
     <row r="252" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H252" s="40"/>
-      <c r="I252" s="40"/>
+      <c r="H252" s="38"/>
+      <c r="I252" s="38"/>
       <c r="J252" s="2"/>
       <c r="K252" s="2"/>
     </row>
     <row r="253" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H253" s="40"/>
-      <c r="I253" s="40"/>
+      <c r="H253" s="38"/>
+      <c r="I253" s="38"/>
       <c r="J253" s="2"/>
       <c r="K253" s="2"/>
     </row>
     <row r="254" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H254" s="40"/>
-      <c r="I254" s="40"/>
+      <c r="H254" s="38"/>
+      <c r="I254" s="38"/>
       <c r="J254" s="2"/>
       <c r="K254" s="2"/>
     </row>
     <row r="255" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H255" s="40"/>
-      <c r="I255" s="40"/>
+      <c r="H255" s="38"/>
+      <c r="I255" s="38"/>
       <c r="J255" s="2"/>
       <c r="K255" s="2"/>
     </row>
     <row r="256" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H256" s="40"/>
-      <c r="I256" s="40"/>
+      <c r="H256" s="38"/>
+      <c r="I256" s="38"/>
       <c r="J256" s="2"/>
       <c r="K256" s="2"/>
     </row>
     <row r="257" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H257" s="40"/>
-      <c r="I257" s="40"/>
+      <c r="H257" s="38"/>
+      <c r="I257" s="38"/>
       <c r="J257" s="2"/>
       <c r="K257" s="2"/>
     </row>
     <row r="258" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H258" s="40"/>
-      <c r="I258" s="40"/>
+      <c r="H258" s="38"/>
+      <c r="I258" s="38"/>
       <c r="J258" s="2"/>
       <c r="K258" s="2"/>
     </row>
     <row r="259" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H259" s="40"/>
-      <c r="I259" s="40"/>
+      <c r="H259" s="38"/>
+      <c r="I259" s="38"/>
       <c r="J259" s="2"/>
       <c r="K259" s="2"/>
     </row>
     <row r="260" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H260" s="40"/>
-      <c r="I260" s="40"/>
+      <c r="H260" s="38"/>
+      <c r="I260" s="38"/>
       <c r="J260" s="2"/>
       <c r="K260" s="2"/>
     </row>
     <row r="261" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H261" s="40"/>
-      <c r="I261" s="40"/>
+      <c r="H261" s="38"/>
+      <c r="I261" s="38"/>
       <c r="J261" s="2"/>
       <c r="K261" s="2"/>
     </row>
     <row r="262" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H262" s="40"/>
-      <c r="I262" s="40"/>
+      <c r="H262" s="38"/>
+      <c r="I262" s="38"/>
       <c r="J262" s="2"/>
       <c r="K262" s="2"/>
     </row>
     <row r="263" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H263" s="40"/>
-      <c r="I263" s="40"/>
+      <c r="H263" s="38"/>
+      <c r="I263" s="38"/>
       <c r="J263" s="2"/>
       <c r="K263" s="2"/>
     </row>
     <row r="264" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H264" s="40"/>
-      <c r="I264" s="40"/>
+      <c r="H264" s="38"/>
+      <c r="I264" s="38"/>
       <c r="J264" s="2"/>
       <c r="K264" s="2"/>
     </row>
     <row r="265" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H265" s="40"/>
-      <c r="I265" s="40"/>
+      <c r="H265" s="38"/>
+      <c r="I265" s="38"/>
       <c r="J265" s="2"/>
       <c r="K265" s="2"/>
     </row>
     <row r="266" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H266" s="40"/>
-      <c r="I266" s="40"/>
+      <c r="H266" s="38"/>
+      <c r="I266" s="38"/>
       <c r="J266" s="2"/>
       <c r="K266" s="2"/>
     </row>
     <row r="267" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H267" s="40"/>
-      <c r="I267" s="40"/>
+      <c r="H267" s="38"/>
+      <c r="I267" s="38"/>
       <c r="J267" s="2"/>
       <c r="K267" s="2"/>
     </row>
@@ -7354,464 +7357,464 @@
       <c r="J393" s="2"/>
     </row>
     <row r="394" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H394" s="40"/>
-      <c r="I394" s="40"/>
+      <c r="H394" s="38"/>
+      <c r="I394" s="38"/>
       <c r="J394" s="2"/>
       <c r="K394" s="2"/>
     </row>
     <row r="395" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H395" s="40"/>
-      <c r="I395" s="40"/>
+      <c r="H395" s="38"/>
+      <c r="I395" s="38"/>
       <c r="J395" s="2"/>
       <c r="K395" s="2"/>
     </row>
     <row r="396" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H396" s="40"/>
-      <c r="I396" s="40"/>
+      <c r="H396" s="38"/>
+      <c r="I396" s="38"/>
       <c r="J396" s="2"/>
       <c r="K396" s="2"/>
     </row>
     <row r="397" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H397" s="40"/>
-      <c r="I397" s="40"/>
+      <c r="H397" s="38"/>
+      <c r="I397" s="38"/>
       <c r="J397" s="2"/>
       <c r="K397" s="2"/>
     </row>
     <row r="398" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H398" s="40"/>
-      <c r="I398" s="40"/>
+      <c r="H398" s="38"/>
+      <c r="I398" s="38"/>
       <c r="J398" s="2"/>
       <c r="K398" s="2"/>
     </row>
     <row r="399" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H399" s="40"/>
-      <c r="I399" s="40"/>
+      <c r="H399" s="38"/>
+      <c r="I399" s="38"/>
       <c r="J399" s="2"/>
       <c r="K399" s="2"/>
     </row>
     <row r="400" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H400" s="40"/>
-      <c r="I400" s="40"/>
+      <c r="H400" s="38"/>
+      <c r="I400" s="38"/>
       <c r="J400" s="2"/>
       <c r="K400" s="2"/>
     </row>
     <row r="401" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H401" s="40"/>
-      <c r="I401" s="40"/>
+      <c r="H401" s="38"/>
+      <c r="I401" s="38"/>
       <c r="J401" s="2"/>
       <c r="K401" s="2"/>
     </row>
     <row r="402" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H402" s="40"/>
-      <c r="I402" s="40"/>
+      <c r="H402" s="38"/>
+      <c r="I402" s="38"/>
       <c r="J402" s="2"/>
       <c r="K402" s="2"/>
     </row>
     <row r="403" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H403" s="40"/>
-      <c r="I403" s="40"/>
+      <c r="H403" s="38"/>
+      <c r="I403" s="38"/>
       <c r="J403" s="2"/>
       <c r="K403" s="2"/>
     </row>
     <row r="404" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H404" s="40"/>
-      <c r="I404" s="40"/>
+      <c r="H404" s="38"/>
+      <c r="I404" s="38"/>
       <c r="J404" s="2"/>
       <c r="K404" s="2"/>
     </row>
     <row r="405" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H405" s="40"/>
-      <c r="I405" s="40"/>
+      <c r="H405" s="38"/>
+      <c r="I405" s="38"/>
       <c r="J405" s="2"/>
       <c r="K405" s="2"/>
     </row>
     <row r="406" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H406" s="40"/>
-      <c r="I406" s="40"/>
+      <c r="H406" s="38"/>
+      <c r="I406" s="38"/>
       <c r="J406" s="2"/>
       <c r="K406" s="2"/>
     </row>
     <row r="407" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H407" s="40"/>
-      <c r="I407" s="40"/>
+      <c r="H407" s="38"/>
+      <c r="I407" s="38"/>
       <c r="J407" s="2"/>
       <c r="K407" s="2"/>
     </row>
     <row r="408" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H408" s="40"/>
-      <c r="I408" s="40"/>
+      <c r="H408" s="38"/>
+      <c r="I408" s="38"/>
       <c r="J408" s="2"/>
       <c r="K408" s="2"/>
     </row>
     <row r="409" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H409" s="40"/>
-      <c r="I409" s="40"/>
+      <c r="H409" s="38"/>
+      <c r="I409" s="38"/>
       <c r="J409" s="2"/>
       <c r="K409" s="2"/>
     </row>
     <row r="410" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H410" s="40"/>
-      <c r="I410" s="40"/>
+      <c r="H410" s="38"/>
+      <c r="I410" s="38"/>
       <c r="J410" s="2"/>
       <c r="K410" s="2"/>
     </row>
     <row r="411" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H411" s="40"/>
-      <c r="I411" s="40"/>
+      <c r="H411" s="38"/>
+      <c r="I411" s="38"/>
       <c r="J411" s="2"/>
       <c r="K411" s="2"/>
     </row>
     <row r="412" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H412" s="40"/>
-      <c r="I412" s="40"/>
+      <c r="H412" s="38"/>
+      <c r="I412" s="38"/>
       <c r="J412" s="2"/>
       <c r="K412" s="2"/>
     </row>
     <row r="413" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H413" s="40"/>
-      <c r="I413" s="40"/>
+      <c r="H413" s="38"/>
+      <c r="I413" s="38"/>
       <c r="J413" s="2"/>
       <c r="K413" s="2"/>
     </row>
     <row r="414" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H414" s="40"/>
-      <c r="I414" s="40"/>
+      <c r="H414" s="38"/>
+      <c r="I414" s="38"/>
       <c r="J414" s="2"/>
       <c r="K414" s="2"/>
     </row>
     <row r="415" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H415" s="40"/>
-      <c r="I415" s="40"/>
+      <c r="H415" s="38"/>
+      <c r="I415" s="38"/>
       <c r="J415" s="2"/>
       <c r="K415" s="2"/>
     </row>
     <row r="416" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H416" s="40"/>
-      <c r="I416" s="40"/>
+      <c r="H416" s="38"/>
+      <c r="I416" s="38"/>
       <c r="J416" s="2"/>
       <c r="K416" s="2"/>
     </row>
     <row r="417" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H417" s="40"/>
-      <c r="I417" s="40"/>
+      <c r="H417" s="38"/>
+      <c r="I417" s="38"/>
       <c r="J417" s="2"/>
       <c r="K417" s="2"/>
     </row>
     <row r="418" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H418" s="40"/>
-      <c r="I418" s="40"/>
+      <c r="H418" s="38"/>
+      <c r="I418" s="38"/>
       <c r="J418" s="2"/>
       <c r="K418" s="2"/>
     </row>
     <row r="419" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H419" s="40"/>
-      <c r="I419" s="40"/>
+      <c r="H419" s="38"/>
+      <c r="I419" s="38"/>
       <c r="J419" s="2"/>
       <c r="K419" s="2"/>
     </row>
     <row r="420" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H420" s="40"/>
-      <c r="I420" s="40"/>
+      <c r="H420" s="38"/>
+      <c r="I420" s="38"/>
       <c r="J420" s="2"/>
       <c r="K420" s="2"/>
     </row>
     <row r="421" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H421" s="40"/>
-      <c r="I421" s="40"/>
+      <c r="H421" s="38"/>
+      <c r="I421" s="38"/>
       <c r="J421" s="2"/>
       <c r="K421" s="2"/>
     </row>
     <row r="422" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H422" s="40"/>
-      <c r="I422" s="40"/>
+      <c r="H422" s="38"/>
+      <c r="I422" s="38"/>
       <c r="J422" s="2"/>
       <c r="K422" s="2"/>
     </row>
     <row r="423" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H423" s="40"/>
-      <c r="I423" s="40"/>
+      <c r="H423" s="38"/>
+      <c r="I423" s="38"/>
       <c r="J423" s="2"/>
       <c r="K423" s="2"/>
     </row>
     <row r="424" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H424" s="40"/>
-      <c r="I424" s="40"/>
+      <c r="H424" s="38"/>
+      <c r="I424" s="38"/>
       <c r="J424" s="2"/>
       <c r="K424" s="2"/>
     </row>
     <row r="425" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H425" s="40"/>
-      <c r="I425" s="40"/>
+      <c r="H425" s="38"/>
+      <c r="I425" s="38"/>
       <c r="J425" s="2"/>
       <c r="K425" s="2"/>
     </row>
     <row r="426" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H426" s="40"/>
-      <c r="I426" s="40"/>
+      <c r="H426" s="38"/>
+      <c r="I426" s="38"/>
       <c r="J426" s="2"/>
       <c r="K426" s="2"/>
     </row>
     <row r="427" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H427" s="40"/>
-      <c r="I427" s="40"/>
+      <c r="H427" s="38"/>
+      <c r="I427" s="38"/>
       <c r="J427" s="2"/>
       <c r="K427" s="2"/>
     </row>
     <row r="428" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H428" s="40"/>
-      <c r="I428" s="40"/>
+      <c r="H428" s="38"/>
+      <c r="I428" s="38"/>
       <c r="J428" s="2"/>
       <c r="K428" s="2"/>
     </row>
     <row r="429" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H429" s="40"/>
-      <c r="I429" s="40"/>
+      <c r="H429" s="38"/>
+      <c r="I429" s="38"/>
       <c r="J429" s="2"/>
       <c r="K429" s="2"/>
     </row>
     <row r="430" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H430" s="40"/>
-      <c r="I430" s="40"/>
+      <c r="H430" s="38"/>
+      <c r="I430" s="38"/>
       <c r="J430" s="2"/>
       <c r="K430" s="2"/>
     </row>
     <row r="431" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H431" s="40"/>
-      <c r="I431" s="40"/>
+      <c r="H431" s="38"/>
+      <c r="I431" s="38"/>
       <c r="J431" s="2"/>
       <c r="K431" s="2"/>
     </row>
     <row r="432" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H432" s="40"/>
-      <c r="I432" s="40"/>
+      <c r="H432" s="38"/>
+      <c r="I432" s="38"/>
       <c r="J432" s="2"/>
       <c r="K432" s="2"/>
     </row>
     <row r="433" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H433" s="40"/>
-      <c r="I433" s="40"/>
+      <c r="H433" s="38"/>
+      <c r="I433" s="38"/>
       <c r="J433" s="2"/>
       <c r="K433" s="2"/>
     </row>
     <row r="434" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H434" s="40"/>
-      <c r="I434" s="40"/>
+      <c r="H434" s="38"/>
+      <c r="I434" s="38"/>
       <c r="J434" s="2"/>
       <c r="K434" s="2"/>
     </row>
     <row r="435" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H435" s="40"/>
-      <c r="I435" s="40"/>
+      <c r="H435" s="38"/>
+      <c r="I435" s="38"/>
       <c r="J435" s="2"/>
       <c r="K435" s="2"/>
     </row>
     <row r="436" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H436" s="40"/>
-      <c r="I436" s="40"/>
+      <c r="H436" s="38"/>
+      <c r="I436" s="38"/>
       <c r="J436" s="2"/>
       <c r="K436" s="2"/>
     </row>
     <row r="437" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H437" s="40"/>
-      <c r="I437" s="40"/>
+      <c r="H437" s="38"/>
+      <c r="I437" s="38"/>
       <c r="J437" s="2"/>
       <c r="K437" s="2"/>
     </row>
     <row r="438" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H438" s="40"/>
-      <c r="I438" s="40"/>
+      <c r="H438" s="38"/>
+      <c r="I438" s="38"/>
       <c r="J438" s="2"/>
       <c r="K438" s="2"/>
     </row>
     <row r="439" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H439" s="40"/>
-      <c r="I439" s="40"/>
+      <c r="H439" s="38"/>
+      <c r="I439" s="38"/>
       <c r="J439" s="2"/>
       <c r="K439" s="2"/>
     </row>
     <row r="440" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H440" s="40"/>
-      <c r="I440" s="40"/>
+      <c r="H440" s="38"/>
+      <c r="I440" s="38"/>
       <c r="J440" s="2"/>
       <c r="K440" s="2"/>
     </row>
     <row r="441" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H441" s="40"/>
-      <c r="I441" s="40"/>
+      <c r="H441" s="38"/>
+      <c r="I441" s="38"/>
       <c r="J441" s="2"/>
       <c r="K441" s="2"/>
     </row>
     <row r="442" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H442" s="40"/>
-      <c r="I442" s="40"/>
+      <c r="H442" s="38"/>
+      <c r="I442" s="38"/>
       <c r="J442" s="2"/>
       <c r="K442" s="2"/>
     </row>
     <row r="443" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H443" s="40"/>
-      <c r="I443" s="40"/>
+      <c r="H443" s="38"/>
+      <c r="I443" s="38"/>
       <c r="J443" s="2"/>
       <c r="K443" s="2"/>
     </row>
     <row r="444" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H444" s="40"/>
-      <c r="I444" s="40"/>
+      <c r="H444" s="38"/>
+      <c r="I444" s="38"/>
       <c r="J444" s="2"/>
       <c r="K444" s="2"/>
     </row>
     <row r="445" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H445" s="40"/>
-      <c r="I445" s="40"/>
+      <c r="H445" s="38"/>
+      <c r="I445" s="38"/>
       <c r="J445" s="2"/>
       <c r="K445" s="2"/>
     </row>
     <row r="446" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H446" s="40"/>
-      <c r="I446" s="40"/>
+      <c r="H446" s="38"/>
+      <c r="I446" s="38"/>
       <c r="J446" s="2"/>
       <c r="K446" s="2"/>
     </row>
     <row r="447" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H447" s="40"/>
-      <c r="I447" s="40"/>
+      <c r="H447" s="38"/>
+      <c r="I447" s="38"/>
       <c r="J447" s="2"/>
       <c r="K447" s="2"/>
     </row>
     <row r="448" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H448" s="40"/>
-      <c r="I448" s="40"/>
+      <c r="H448" s="38"/>
+      <c r="I448" s="38"/>
       <c r="J448" s="2"/>
       <c r="K448" s="2"/>
     </row>
     <row r="449" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H449" s="40"/>
-      <c r="I449" s="40"/>
+      <c r="H449" s="38"/>
+      <c r="I449" s="38"/>
       <c r="J449" s="2"/>
       <c r="K449" s="2"/>
     </row>
     <row r="450" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H450" s="40"/>
-      <c r="I450" s="40"/>
+      <c r="H450" s="38"/>
+      <c r="I450" s="38"/>
       <c r="J450" s="2"/>
       <c r="K450" s="2"/>
     </row>
     <row r="451" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H451" s="40"/>
-      <c r="I451" s="40"/>
+      <c r="H451" s="38"/>
+      <c r="I451" s="38"/>
       <c r="J451" s="2"/>
       <c r="K451" s="2"/>
     </row>
     <row r="452" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H452" s="40"/>
-      <c r="I452" s="40"/>
+      <c r="H452" s="38"/>
+      <c r="I452" s="38"/>
       <c r="J452" s="2"/>
       <c r="K452" s="2"/>
     </row>
     <row r="453" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H453" s="40"/>
-      <c r="I453" s="40"/>
+      <c r="H453" s="38"/>
+      <c r="I453" s="38"/>
       <c r="J453" s="2"/>
       <c r="K453" s="2"/>
     </row>
     <row r="454" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H454" s="40"/>
-      <c r="I454" s="40"/>
+      <c r="H454" s="38"/>
+      <c r="I454" s="38"/>
       <c r="J454" s="2"/>
       <c r="K454" s="2"/>
     </row>
     <row r="455" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H455" s="40"/>
-      <c r="I455" s="40"/>
+      <c r="H455" s="38"/>
+      <c r="I455" s="38"/>
       <c r="J455" s="2"/>
       <c r="K455" s="2"/>
     </row>
     <row r="456" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H456" s="40"/>
-      <c r="I456" s="40"/>
+      <c r="H456" s="38"/>
+      <c r="I456" s="38"/>
       <c r="J456" s="2"/>
       <c r="K456" s="2"/>
     </row>
     <row r="457" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H457" s="40"/>
-      <c r="I457" s="40"/>
+      <c r="H457" s="38"/>
+      <c r="I457" s="38"/>
       <c r="J457" s="2"/>
       <c r="K457" s="2"/>
     </row>
     <row r="458" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H458" s="40"/>
-      <c r="I458" s="40"/>
+      <c r="H458" s="38"/>
+      <c r="I458" s="38"/>
       <c r="J458" s="2"/>
       <c r="K458" s="2"/>
     </row>
     <row r="459" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H459" s="40"/>
-      <c r="I459" s="40"/>
+      <c r="H459" s="38"/>
+      <c r="I459" s="38"/>
       <c r="J459" s="2"/>
       <c r="K459" s="2"/>
     </row>
     <row r="460" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H460" s="40"/>
-      <c r="I460" s="40"/>
+      <c r="H460" s="38"/>
+      <c r="I460" s="38"/>
       <c r="J460" s="2"/>
       <c r="K460" s="2"/>
     </row>
     <row r="461" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H461" s="40"/>
-      <c r="I461" s="40"/>
+      <c r="H461" s="38"/>
+      <c r="I461" s="38"/>
       <c r="J461" s="2"/>
       <c r="K461" s="2"/>
     </row>
     <row r="462" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H462" s="40"/>
-      <c r="I462" s="40"/>
+      <c r="H462" s="38"/>
+      <c r="I462" s="38"/>
       <c r="J462" s="2"/>
       <c r="K462" s="2"/>
     </row>
     <row r="463" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H463" s="40"/>
-      <c r="I463" s="40"/>
+      <c r="H463" s="38"/>
+      <c r="I463" s="38"/>
       <c r="J463" s="2"/>
       <c r="K463" s="2"/>
     </row>
     <row r="464" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H464" s="40"/>
-      <c r="I464" s="40"/>
+      <c r="H464" s="38"/>
+      <c r="I464" s="38"/>
       <c r="J464" s="2"/>
       <c r="K464" s="2"/>
     </row>
     <row r="465" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H465" s="40"/>
-      <c r="I465" s="40"/>
+      <c r="H465" s="38"/>
+      <c r="I465" s="38"/>
       <c r="J465" s="2"/>
       <c r="K465" s="2"/>
     </row>
     <row r="466" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H466" s="40"/>
-      <c r="I466" s="40"/>
+      <c r="H466" s="38"/>
+      <c r="I466" s="38"/>
       <c r="J466" s="2"/>
       <c r="K466" s="2"/>
     </row>
     <row r="467" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H467" s="40"/>
-      <c r="I467" s="40"/>
+      <c r="H467" s="38"/>
+      <c r="I467" s="38"/>
       <c r="J467" s="2"/>
       <c r="K467" s="2"/>
     </row>
     <row r="468" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H468" s="40"/>
-      <c r="I468" s="40"/>
+      <c r="H468" s="38"/>
+      <c r="I468" s="38"/>
       <c r="J468" s="2"/>
       <c r="K468" s="2"/>
     </row>
     <row r="469" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H469" s="40"/>
-      <c r="I469" s="40"/>
+      <c r="H469" s="38"/>
+      <c r="I469" s="38"/>
       <c r="J469" s="2"/>
       <c r="K469" s="2"/>
     </row>
     <row r="470" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H470" s="40"/>
-      <c r="I470" s="40"/>
+      <c r="H470" s="38"/>
+      <c r="I470" s="38"/>
       <c r="J470" s="2"/>
       <c r="K470" s="2"/>
     </row>
@@ -8197,92 +8200,92 @@
       <c r="J597" s="2"/>
     </row>
     <row r="598" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H598" s="40"/>
-      <c r="I598" s="40"/>
+      <c r="H598" s="38"/>
+      <c r="I598" s="38"/>
       <c r="J598" s="2"/>
       <c r="K598" s="2"/>
     </row>
     <row r="599" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H599" s="40"/>
-      <c r="I599" s="40"/>
+      <c r="H599" s="38"/>
+      <c r="I599" s="38"/>
       <c r="J599" s="2"/>
       <c r="K599" s="2"/>
     </row>
     <row r="600" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H600" s="40"/>
-      <c r="I600" s="40"/>
+      <c r="H600" s="38"/>
+      <c r="I600" s="38"/>
       <c r="J600" s="2"/>
       <c r="K600" s="2"/>
     </row>
     <row r="601" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H601" s="40"/>
-      <c r="I601" s="40"/>
+      <c r="H601" s="38"/>
+      <c r="I601" s="38"/>
       <c r="J601" s="2"/>
       <c r="K601" s="2"/>
     </row>
     <row r="602" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H602" s="40"/>
-      <c r="I602" s="40"/>
+      <c r="H602" s="38"/>
+      <c r="I602" s="38"/>
       <c r="J602" s="2"/>
       <c r="K602" s="2"/>
     </row>
     <row r="603" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H603" s="40"/>
-      <c r="I603" s="40"/>
+      <c r="H603" s="38"/>
+      <c r="I603" s="38"/>
       <c r="J603" s="2"/>
       <c r="K603" s="2"/>
     </row>
     <row r="604" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H604" s="40"/>
-      <c r="I604" s="40"/>
+      <c r="H604" s="38"/>
+      <c r="I604" s="38"/>
       <c r="J604" s="2"/>
       <c r="K604" s="2"/>
     </row>
     <row r="605" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H605" s="40"/>
-      <c r="I605" s="40"/>
+      <c r="H605" s="38"/>
+      <c r="I605" s="38"/>
       <c r="J605" s="2"/>
       <c r="K605" s="2"/>
     </row>
     <row r="606" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H606" s="40"/>
-      <c r="I606" s="40"/>
+      <c r="H606" s="38"/>
+      <c r="I606" s="38"/>
       <c r="J606" s="2"/>
       <c r="K606" s="2"/>
     </row>
     <row r="607" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H607" s="40"/>
-      <c r="I607" s="40"/>
+      <c r="H607" s="38"/>
+      <c r="I607" s="38"/>
       <c r="J607" s="2"/>
       <c r="K607" s="2"/>
     </row>
     <row r="608" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H608" s="40"/>
-      <c r="I608" s="40"/>
+      <c r="H608" s="38"/>
+      <c r="I608" s="38"/>
       <c r="J608" s="2"/>
       <c r="K608" s="2"/>
     </row>
     <row r="609" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H609" s="40"/>
-      <c r="I609" s="40"/>
+      <c r="H609" s="38"/>
+      <c r="I609" s="38"/>
       <c r="J609" s="2"/>
       <c r="K609" s="2"/>
     </row>
     <row r="610" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H610" s="40"/>
-      <c r="I610" s="40"/>
+      <c r="H610" s="38"/>
+      <c r="I610" s="38"/>
       <c r="J610" s="2"/>
       <c r="K610" s="2"/>
     </row>
     <row r="611" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H611" s="40"/>
-      <c r="I611" s="40"/>
+      <c r="H611" s="38"/>
+      <c r="I611" s="38"/>
       <c r="J611" s="2"/>
       <c r="K611" s="2"/>
     </row>
     <row r="612" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H612" s="40"/>
-      <c r="I612" s="40"/>
+      <c r="H612" s="38"/>
+      <c r="I612" s="38"/>
       <c r="J612" s="2"/>
       <c r="K612" s="2"/>
     </row>
@@ -8299,100 +8302,66 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18060591-A3C9-C445-BFA2-21AF541357A2}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.1640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.1640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.83203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="12.83203125" style="54"/>
+    <col min="1" max="1" width="7.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.1640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="12.83203125" style="52"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="61" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="61" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="62" t="s">
-        <v>53</v>
+      <c r="E1" s="57" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>113</v>
+      <c r="A2" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" s="56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="56" t="s">
-        <v>113</v>
+      <c r="B3" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -8416,19 +8385,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>6</v>
+      <c r="A1" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>101</v>
+      <c r="A2" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
